--- a/site/exports/scu-cs.xlsx
+++ b/site/exports/scu-cs.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="R2fb1839ee3ba400c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rbfd98fb87eed4eff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Rb433eb7778f140c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rb93863e03f7f4af5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R92007035a7254df4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="总览" sheetId="1" r:id="Rec06fca645584297"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="经历" sheetId="2" r:id="Rb4e192cf9ede4d67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导师" sheetId="3" r:id="Ra5730afd0ea34e18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="论文" sheetId="4" r:id="Rc3227ef80c524cc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="来源" sheetId="5" r:id="R8e2a293905ab429c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -139,7 +139,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T35_0" displayName="T35_0" ref="A1:K2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T38_0" displayName="T38_0" ref="A1:K4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="11">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="校区"/>
@@ -158,7 +158,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T35_1" displayName="T35_1" ref="A1:S5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="T38_1" displayName="T38_1" ref="A1:S14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="19">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="事件类型"/>
@@ -185,7 +185,27 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T35_3" displayName="T35_3" ref="A1:L2" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="T38_2" displayName="T38_2" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="12">
+    <x:tableColumn id="1" name="姓名"/>
+    <x:tableColumn id="2" name="导师姓名"/>
+    <x:tableColumn id="3" name="关系类型"/>
+    <x:tableColumn id="4" name="阶段"/>
+    <x:tableColumn id="5" name="简介"/>
+    <x:tableColumn id="6" name="在职状态"/>
+    <x:tableColumn id="7" name="状态说明"/>
+    <x:tableColumn id="8" name="已核在职主页"/>
+    <x:tableColumn id="9" name="关系来源"/>
+    <x:tableColumn id="10" name="任职来源"/>
+    <x:tableColumn id="11" name="所属学校ID"/>
+    <x:tableColumn id="12" name="所属学校"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T38_3" displayName="T38_3" ref="A1:L3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="标题"/>
@@ -204,8 +224,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="T35_4" displayName="T35_4" ref="A1:G6" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="T38_4" displayName="T38_4" ref="A1:G12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="姓名"/>
     <x:tableColumn id="2" name="来源ID"/>
@@ -495,10 +515,76 @@
         <x:v>四川大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>陈黎</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>计算机学院（软件学院、智能科学与技术学院）</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenli12/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>仅公开职业资料，未核字段保留空值。；精选书目非全集，官网列示未逐篇出版者核验。；本人导师及逐篇书目未查得。</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str"/>
+      <x:c r="J3" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="64" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>校区未标注</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>计算机学院（软件学院、智能科学与技术学院）</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="E4" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>仅公开职业资料，未核字段保留空值。；精选书目非全集，官网列示未逐篇出版者核验。；本科硕士未披露，导师现职状态未知；科研导师不等于学位导师。</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>分批核实资料，不是完整名录</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>公开个人页（时效以核对日为准）</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str"/>
+      <x:c r="J4" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="K4" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R20d6ab284e6e41d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R99fd75ebf0ce4192"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -765,10 +851,409 @@
         <x:v>四川大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="6" ht="64" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>陈黎</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>学士</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>重庆建筑大学</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>1995-09</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>1999-07</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str"/>
+      <x:c r="H6" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K6" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L6" s="6" t="str"/>
+      <x:c r="M6" s="7" t="str"/>
+      <x:c r="N6" s="6" t="str"/>
+      <x:c r="O6" s="6" t="str">
+        <x:v>本人履历仅学位标签与区间，没有明确获授语句；院系名未直接推专业。 历史重庆建筑大学不直接套合并后重庆大学985属性。</x:v>
+      </x:c>
+      <x:c r="P6" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q6" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenli12/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R6" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S6" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>陈黎</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>硕士</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>重庆大学</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>1999-09</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>2002-03</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str"/>
+      <x:c r="H7" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K7" s="6" t="str">
+        <x:v>yes</x:v>
+      </x:c>
+      <x:c r="L7" s="6" t="str"/>
+      <x:c r="M7" s="7" t="str"/>
+      <x:c r="N7" s="6" t="str"/>
+      <x:c r="O7" s="6" t="str">
+        <x:v>本人履历仅学位标签与区间，没有明确获授语句；院系名未直接推专业。</x:v>
+      </x:c>
+      <x:c r="P7" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q7" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenli12/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R7" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S7" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>陈黎</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>2004-09</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>2010-07</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str"/>
+      <x:c r="H8" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L8" s="6" t="str"/>
+      <x:c r="M8" s="7" t="str"/>
+      <x:c r="N8" s="6" t="str"/>
+      <x:c r="O8" s="6" t="str">
+        <x:v>本人履历仅学位标签与区间，没有明确获授语句；院系名未直接推专业。</x:v>
+      </x:c>
+      <x:c r="P8" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q8" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenli12/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R8" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S8" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>陈黎</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>讲师</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>四川大学计算机学院（软件学院、智能科学与技术学院）</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str"/>
+      <x:c r="F9" s="6" t="str"/>
+      <x:c r="G9" s="6" t="str"/>
+      <x:c r="H9" s="6" t="str"/>
+      <x:c r="I9" s="6" t="str"/>
+      <x:c r="J9" s="6" t="str"/>
+      <x:c r="K9" s="6" t="str"/>
+      <x:c r="L9" s="6" t="str"/>
+      <x:c r="M9" s="7" t="str"/>
+      <x:c r="N9" s="6" t="str"/>
+      <x:c r="O9" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P9" s="6" t="str"/>
+      <x:c r="Q9" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/xyjs.jsp?id=1035&amp;lang=zh_CN&amp;st=0&amp;urltype=tsites.CollegeTeacherList&amp;wbtreeid=1012</x:v>
+      </x:c>
+      <x:c r="R9" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S9" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>degree_study</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>2004-09</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>2008-07</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str"/>
+      <x:c r="H10" s="6" t="str">
+        <x:v>中国</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str">
+        <x:v>中国内地</x:v>
+      </x:c>
+      <x:c r="J10" s="6" t="str">
+        <x:v>亚洲</x:v>
+      </x:c>
+      <x:c r="K10" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="L10" s="6" t="str"/>
+      <x:c r="M10" s="7" t="str"/>
+      <x:c r="N10" s="6" t="str"/>
+      <x:c r="O10" s="6" t="str">
+        <x:v>原文计算机学院/博，未明确获授。</x:v>
+      </x:c>
+      <x:c r="P10" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q10" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R10" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S10" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>professional_research</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str"/>
+      <x:c r="D11" s="6" t="str">
+        <x:v>明尼苏达大学</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>2009-08</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>2010-09</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str"/>
+      <x:c r="H11" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str">
+        <x:v>美国</x:v>
+      </x:c>
+      <x:c r="J11" s="6" t="str">
+        <x:v>北美洲</x:v>
+      </x:c>
+      <x:c r="K11" s="6" t="str">
+        <x:v>no</x:v>
+      </x:c>
+      <x:c r="L11" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M11" s="7" t="str"/>
+      <x:c r="N11" s="6" t="str"/>
+      <x:c r="O11" s="6" t="str">
+        <x:v>明确在电子和计算机工程系研究及导师，未写博士后或访问身份，不补具体头衔。</x:v>
+      </x:c>
+      <x:c r="P11" s="6" t="str">
+        <x:v>按来源所指院校所在地标准化，不代表国籍；授位地点与访问、攻读未获学位、联合培养分开。</x:v>
+      </x:c>
+      <x:c r="Q11" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R11" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S11" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>教授</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>四川大学计算机学院（软件学院、智能科学与技术学院）</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str"/>
+      <x:c r="F12" s="6" t="str"/>
+      <x:c r="G12" s="6" t="str"/>
+      <x:c r="H12" s="6" t="str"/>
+      <x:c r="I12" s="6" t="str"/>
+      <x:c r="J12" s="6" t="str"/>
+      <x:c r="K12" s="6" t="str"/>
+      <x:c r="L12" s="6" t="str"/>
+      <x:c r="M12" s="7" t="str"/>
+      <x:c r="N12" s="6" t="str"/>
+      <x:c r="O12" s="6" t="str">
+        <x:v>现行官方名录列示；不代表独立人事在岗核验，起始年月未知。</x:v>
+      </x:c>
+      <x:c r="P12" s="6" t="str"/>
+      <x:c r="Q12" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/xyjs.jsp?id=1035&amp;lang=zh_CN&amp;st=0&amp;urltype=tsites.CollegeTeacherList&amp;wbtreeid=1012</x:v>
+      </x:c>
+      <x:c r="R12" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S12" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="64" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>物联网系主任</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>四川大学计算机学院</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str"/>
+      <x:c r="F13" s="6" t="str"/>
+      <x:c r="G13" s="6" t="str"/>
+      <x:c r="H13" s="6" t="str"/>
+      <x:c r="I13" s="6" t="str"/>
+      <x:c r="J13" s="6" t="str"/>
+      <x:c r="K13" s="6" t="str"/>
+      <x:c r="L13" s="6" t="str"/>
+      <x:c r="M13" s="7" t="str"/>
+      <x:c r="N13" s="6" t="str"/>
+      <x:c r="O13" s="6" t="str"/>
+      <x:c r="P13" s="6" t="str"/>
+      <x:c r="Q13" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R13" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S13" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="64" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>employment</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>物联网实验室负责人</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>四川大学计算机学院</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str"/>
+      <x:c r="F14" s="6" t="str"/>
+      <x:c r="G14" s="6" t="str"/>
+      <x:c r="H14" s="6" t="str"/>
+      <x:c r="I14" s="6" t="str"/>
+      <x:c r="J14" s="6" t="str"/>
+      <x:c r="K14" s="6" t="str"/>
+      <x:c r="L14" s="6" t="str"/>
+      <x:c r="M14" s="7" t="str"/>
+      <x:c r="N14" s="6" t="str"/>
+      <x:c r="O14" s="6" t="str"/>
+      <x:c r="P14" s="6" t="str"/>
+      <x:c r="Q14" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="R14" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="S14" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54b6a6b5001a440a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd09c6058ec044c67"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -829,8 +1314,79 @@
         <x:v>所属学校</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" ht="64" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>李志蜀</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>博士导师</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>博士</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>本人履历明确博士导师李志蜀教授，四川大学；现职/退休状态未核。</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>当前在职状态未知，不按年龄或旧头衔推断。</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str"/>
+      <x:c r="I2" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str"/>
+      <x:c r="K2" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="L2" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Tian He</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>职业科研指导（非学位）</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>非学位科研</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>本人履历明确明尼苏达大学研究阶段导师Tian He；与博士指导分开，不合并同名化学/器件学者。</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>unknown</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>职业科研指导（非学位）；research_supervisor；professional_research_advisor；指导起止：起始时间未披露 至 结束时间未披露；对应非学位科研经历：scu-chenliangyin-education-2；明尼苏达大学；2009-08 至 2010-09（经历区间，不等于指导起止；非博士后认定）；明尼苏达个人站读取502，现职未知，不提供已核在职导航。；直接证实的非学位职业科研指导，保留原科研事件绑定，不等于博士后或学位导师；指导起止仍未知，不借用科研事件日期。；独立职业指导，不计入学位师承图；已核职业指导计数：1</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str"/>
+      <x:c r="I3" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str"/>
+      <x:c r="K3" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R104cebc1bd374a1e"/>
+  </x:tableParts>
 </x:worksheet>
 </file>
 
@@ -926,10 +1482,46 @@
         <x:v>四川大学</x:v>
       </x:c>
     </x:row>
+    <x:row r="3" ht="64" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Group-based Neighbor Discovery in Low-duty-cycle Mobile Sensor Networks</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="n">
+        <x:v>2016</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str"/>
+      <x:c r="E3" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>期刊论文；journal_article</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str">
+        <x:v>仅官方精选书目已核，未逐篇核实出版社落地页或全文。；official_publication_list_only</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str">
+        <x:v>官网15(8):1996–2009，仅精选书目。</x:v>
+      </x:c>
+      <x:c r="K3" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="L3" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7c7c824a07d4f8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf3c4b6b47594efc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1041,16 +1633,16 @@
     </x:row>
     <x:row r="5" ht="64" customHeight="1">
       <x:c r="A5" s="6" t="str">
-        <x:v>陈虎</x:v>
+        <x:v>陈黎</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>institution-classification-3</x:v>
+        <x:v>chenli12-source-1</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>https://www.uestc.edu.cn/xxgk/xxls.htm</x:v>
+        <x:v>https://faculty.scu.edu.cn/xyjs.jsp?id=1035&amp;lang=zh_CN&amp;st=0&amp;urltype=tsites.CollegeTeacherList&amp;wbtreeid=1012</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
       </x:c>
       <x:c r="E5" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -1064,16 +1656,16 @@
     </x:row>
     <x:row r="6" ht="64" customHeight="1">
       <x:c r="A6" s="6" t="str">
-        <x:v>陈虎</x:v>
+        <x:v>陈黎</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>institution-classification-4</x:v>
+        <x:v>chenli12-source-2</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+        <x:v>https://faculty.scu.edu.cn/chenli12/zh_CN/index.htm</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
       </x:c>
       <x:c r="E6" s="7" t="d">
         <x:v>2026-10-23T00:00:00.000Z</x:v>
@@ -1082,13 +1674,151 @@
         <x:v>scu</x:v>
       </x:c>
       <x:c r="G6" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="64" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>chenliangyin-source-1</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/xyjs.jsp?id=1035&amp;lang=zh_CN&amp;st=0&amp;urltype=tsites.CollegeTeacherList&amp;wbtreeid=1012</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>官方名录内容已读，仅保存本批选中观察。；official_roster_read</x:v>
+      </x:c>
+      <x:c r="E7" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="64" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>chenliangyin-source-2</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>https://faculty.scu.edu.cn/chenliangyin/zh_CN/index.htm</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>官方公开正文已读，仅覆盖已审字段。；official_public_body_read</x:v>
+      </x:c>
+      <x:c r="E8" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="64" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>陈虎</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>institution-classification-3</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>https://www.uestc.edu.cn/xxgk/xxls.htm</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E9" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="64" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>陈虎</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>institution-classification-4</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E10" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="64" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>陈黎</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>https://www.cqu.edu.cn/xqgk/xxjj.htm</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E11" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>四川大学</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="64" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>陈良银</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>institution-classification-2</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>https://www.moe.gov.cn/srcsite/A22/s7065/200612/t20061206_128833.html</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>历史985院校分类参考；非个人授位或就读当年建设身份的证明</x:v>
+      </x:c>
+      <x:c r="E12" s="7" t="d">
+        <x:v>2026-10-23T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>scu</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
         <x:v>四川大学</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re431a18835ca4ab9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1eae9a818920497a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/site/exports/scu-cs.xlsx
+++ b/site/exports/scu-cs.xlsx
@@ -452,8 +452,8 @@
     <col width="65" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="65" customWidth="1" min="6" max="6"/>
-    <col width="18.2" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="37.8" customWidth="1" min="7" max="7"/>
+    <col width="26.6" customWidth="1" min="8" max="8"/>
     <col width="21" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -482,7 +482,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>核对日期</t>
+          <t>已记录来源检索日期</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr"/>
@@ -602,12 +602,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr"/>
@@ -655,12 +655,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>分批核实资料，不是完整名录</t>
+          <t>分批核实资料，不是完整名录；人物整体核验日期未单独记录</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>公开个人页（时效以核对日为准）</t>
+          <t>公开个人页（访问与内容时效见来源记录）</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr"/>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23</t>
+          <t>未单独记录</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
